--- a/baseball/lineups/2026-03-22-bracket-play.xlsx
+++ b/baseball/lineups/2026-03-22-bracket-play.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="B1 vs Flash-Garrett" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="B3 vs Cincinnati Raiders" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Wed vs Raiders" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -87,6 +88,12 @@
       <color rgb="00555555"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -131,7 +138,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -153,11 +160,69 @@
         <color rgb="00D0D0D0"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00DDDDDD"/>
+      </left>
+      <right style="thin">
+        <color rgb="00DDDDDD"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DDDDDD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DDDDDD"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00DDDDDD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00DDDDDD"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DDDDDD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00DDDDDD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DDDDDD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00DDDDDD"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DDDDDD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DDDDDD"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -199,6 +264,31 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -564,7 +654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H58"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -597,13 +687,6 @@
           <t>1:30 time limit — expect 4-5 innings, 6th unlikely</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="n"/>
-      <c r="F3" s="4" t="n"/>
-      <c r="G3" s="4" t="n"/>
-      <c r="H3" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -618,13 +701,6 @@
           <t>Porter Mills (Inn 1-2) → Lukas Adams (Inn 3-4) → Charlie Ruther (Inn 5-6 if needed)</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n"/>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
-      <c r="E6" s="7" t="n"/>
-      <c r="F6" s="7" t="n"/>
-      <c r="G6" s="7" t="n"/>
-      <c r="H6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
@@ -632,13 +708,6 @@
           <t>CATCHING: Charlie Ruther catches Inn 1-4 | Mason Floyd catches Inn 5-6 (when Charlie pitches)</t>
         </is>
       </c>
-      <c r="B7" s="9" t="n"/>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="9" t="n"/>
-      <c r="E7" s="9" t="n"/>
-      <c r="F7" s="9" t="n"/>
-      <c r="G7" s="9" t="n"/>
-      <c r="H7" s="9" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -1479,56 +1548,474 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
+          <t>ROSTER CHECK</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="21" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="B54" s="21" t="inlineStr">
+        <is>
+          <t>Inning 1</t>
+        </is>
+      </c>
+      <c r="C54" s="21" t="inlineStr">
+        <is>
+          <t>Inning 2</t>
+        </is>
+      </c>
+      <c r="D54" s="21" t="inlineStr">
+        <is>
+          <t>Inning 3</t>
+        </is>
+      </c>
+      <c r="E54" s="21" t="inlineStr">
+        <is>
+          <t>Inning 4</t>
+        </is>
+      </c>
+      <c r="F54" s="21" t="inlineStr">
+        <is>
+          <t>Inning 5 *</t>
+        </is>
+      </c>
+      <c r="G54" s="21" t="inlineStr">
+        <is>
+          <t>Inning 6 *</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="22" t="inlineStr">
+        <is>
+          <t>Porter</t>
+        </is>
+      </c>
+      <c r="B55" s="23">
+        <f>IF(COUNTIF(B$25:B$35,$A55)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="C55" s="23">
+        <f>IF(COUNTIF(C$25:C$35,$A55)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="D55" s="23">
+        <f>IF(COUNTIF(D$25:D$35,$A55)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="E55" s="23">
+        <f>IF(COUNTIF(E$25:E$35,$A55)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="F55" s="23">
+        <f>IF(COUNTIF(F$25:F$35,$A55)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="G55" s="23">
+        <f>IF(COUNTIF(G$25:G$35,$A55)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="22" t="inlineStr">
+        <is>
+          <t>Zack</t>
+        </is>
+      </c>
+      <c r="B56" s="23">
+        <f>IF(COUNTIF(B$25:B$35,$A56)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="C56" s="23">
+        <f>IF(COUNTIF(C$25:C$35,$A56)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="D56" s="23">
+        <f>IF(COUNTIF(D$25:D$35,$A56)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="E56" s="23">
+        <f>IF(COUNTIF(E$25:E$35,$A56)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="F56" s="23">
+        <f>IF(COUNTIF(F$25:F$35,$A56)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="G56" s="23">
+        <f>IF(COUNTIF(G$25:G$35,$A56)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="22" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="B57" s="23">
+        <f>IF(COUNTIF(B$25:B$35,$A57)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="C57" s="23">
+        <f>IF(COUNTIF(C$25:C$35,$A57)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="D57" s="23">
+        <f>IF(COUNTIF(D$25:D$35,$A57)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="E57" s="23">
+        <f>IF(COUNTIF(E$25:E$35,$A57)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="F57" s="23">
+        <f>IF(COUNTIF(F$25:F$35,$A57)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="G57" s="23">
+        <f>IF(COUNTIF(G$25:G$35,$A57)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="22" t="inlineStr">
+        <is>
+          <t>Crew</t>
+        </is>
+      </c>
+      <c r="B58" s="23">
+        <f>IF(COUNTIF(B$25:B$35,$A58)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="C58" s="23">
+        <f>IF(COUNTIF(C$25:C$35,$A58)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="D58" s="23">
+        <f>IF(COUNTIF(D$25:D$35,$A58)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="E58" s="23">
+        <f>IF(COUNTIF(E$25:E$35,$A58)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="F58" s="23">
+        <f>IF(COUNTIF(F$25:F$35,$A58)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="G58" s="23">
+        <f>IF(COUNTIF(G$25:G$35,$A58)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="22" t="inlineStr">
+        <is>
+          <t>Grayson</t>
+        </is>
+      </c>
+      <c r="B59" s="23">
+        <f>IF(COUNTIF(B$25:B$35,$A59)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="C59" s="23">
+        <f>IF(COUNTIF(C$25:C$35,$A59)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="D59" s="23">
+        <f>IF(COUNTIF(D$25:D$35,$A59)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="E59" s="23">
+        <f>IF(COUNTIF(E$25:E$35,$A59)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="F59" s="23">
+        <f>IF(COUNTIF(F$25:F$35,$A59)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="G59" s="23">
+        <f>IF(COUNTIF(G$25:G$35,$A59)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="22" t="inlineStr">
+        <is>
+          <t>Lasita</t>
+        </is>
+      </c>
+      <c r="B60" s="23">
+        <f>IF(COUNTIF(B$25:B$35,$A60)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="C60" s="23">
+        <f>IF(COUNTIF(C$25:C$35,$A60)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="D60" s="23">
+        <f>IF(COUNTIF(D$25:D$35,$A60)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="E60" s="23">
+        <f>IF(COUNTIF(E$25:E$35,$A60)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="F60" s="23">
+        <f>IF(COUNTIF(F$25:F$35,$A60)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="G60" s="23">
+        <f>IF(COUNTIF(G$25:G$35,$A60)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="22" t="inlineStr">
+        <is>
+          <t>Lukas</t>
+        </is>
+      </c>
+      <c r="B61" s="23">
+        <f>IF(COUNTIF(B$25:B$35,$A61)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="C61" s="23">
+        <f>IF(COUNTIF(C$25:C$35,$A61)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="D61" s="23">
+        <f>IF(COUNTIF(D$25:D$35,$A61)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="E61" s="23">
+        <f>IF(COUNTIF(E$25:E$35,$A61)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="F61" s="23">
+        <f>IF(COUNTIF(F$25:F$35,$A61)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="G61" s="23">
+        <f>IF(COUNTIF(G$25:G$35,$A61)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="22" t="inlineStr">
+        <is>
+          <t>Mason</t>
+        </is>
+      </c>
+      <c r="B62" s="23">
+        <f>IF(COUNTIF(B$25:B$35,$A62)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="C62" s="23">
+        <f>IF(COUNTIF(C$25:C$35,$A62)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="D62" s="23">
+        <f>IF(COUNTIF(D$25:D$35,$A62)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="E62" s="23">
+        <f>IF(COUNTIF(E$25:E$35,$A62)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="F62" s="23">
+        <f>IF(COUNTIF(F$25:F$35,$A62)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="G62" s="23">
+        <f>IF(COUNTIF(G$25:G$35,$A62)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="22" t="inlineStr">
+        <is>
+          <t>Kayson</t>
+        </is>
+      </c>
+      <c r="B63" s="23">
+        <f>IF(COUNTIF(B$25:B$35,$A63)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="C63" s="23">
+        <f>IF(COUNTIF(C$25:C$35,$A63)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="D63" s="23">
+        <f>IF(COUNTIF(D$25:D$35,$A63)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="E63" s="23">
+        <f>IF(COUNTIF(E$25:E$35,$A63)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="F63" s="23">
+        <f>IF(COUNTIF(F$25:F$35,$A63)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="G63" s="23">
+        <f>IF(COUNTIF(G$25:G$35,$A63)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="22" t="inlineStr">
+        <is>
+          <t>Owen</t>
+        </is>
+      </c>
+      <c r="B64" s="23">
+        <f>IF(COUNTIF(B$25:B$35,$A64)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="C64" s="23">
+        <f>IF(COUNTIF(C$25:C$35,$A64)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="D64" s="23">
+        <f>IF(COUNTIF(D$25:D$35,$A64)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="E64" s="23">
+        <f>IF(COUNTIF(E$25:E$35,$A64)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="F64" s="23">
+        <f>IF(COUNTIF(F$25:F$35,$A64)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="G64" s="23">
+        <f>IF(COUNTIF(G$25:G$35,$A64)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="22" t="inlineStr">
+        <is>
+          <t>Charlie</t>
+        </is>
+      </c>
+      <c r="B65" s="23">
+        <f>IF(COUNTIF(B$25:B$35,$A65)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="C65" s="23">
+        <f>IF(COUNTIF(C$25:C$35,$A65)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="D65" s="23">
+        <f>IF(COUNTIF(D$25:D$35,$A65)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="E65" s="23">
+        <f>IF(COUNTIF(E$25:E$35,$A65)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="F65" s="23">
+        <f>IF(COUNTIF(F$25:F$35,$A65)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="G65" s="23">
+        <f>IF(COUNTIF(G$25:G$35,$A65)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="24" t="inlineStr">
+        <is>
+          <t>Missing Count</t>
+        </is>
+      </c>
+      <c r="B66" s="25">
+        <f>COUNTIF(B55:B65,"MISSING")</f>
+        <v/>
+      </c>
+      <c r="C66" s="25">
+        <f>COUNTIF(C55:C65,"MISSING")</f>
+        <v/>
+      </c>
+      <c r="D66" s="25">
+        <f>COUNTIF(D55:D65,"MISSING")</f>
+        <v/>
+      </c>
+      <c r="E66" s="25">
+        <f>COUNTIF(E55:E65,"MISSING")</f>
+        <v/>
+      </c>
+      <c r="F66" s="25">
+        <f>COUNTIF(F55:F65,"MISSING")</f>
+        <v/>
+      </c>
+      <c r="G66" s="25">
+        <f>COUNTIF(G55:G65,"MISSING")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="26" t="inlineStr">
+        <is>
+          <t>(Each inning should have exactly 2 missing = bench)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
           <t>NOTES</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="20" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="20" t="inlineStr">
         <is>
           <t>• 1:30 time limit — best pitchers front-loaded in innings 1-4</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="20" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="20" t="inlineStr">
         <is>
           <t>• No player sits more than 2 innings | No player sits back-to-back</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="20" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="20" t="inlineStr">
         <is>
           <t>• Charlie behind the plate for stealing situations (9U live stealing)</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="20" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="20" t="inlineStr">
         <is>
           <t>• Batting order stays the same regardless of field position</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="20" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="20" t="inlineStr">
         <is>
           <t>• Porter (#2 pitcher) + Lukas (#3) handle this game — Zack saved for Raiders</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="7">
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A56:H56"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A55:H55"/>
     <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A57:H57"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A54:H54"/>
-    <mergeCell ref="A58:H58"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="A37:H37"/>
     <mergeCell ref="A6:H6"/>
@@ -1543,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H58"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1576,13 +2063,6 @@
           <t>1:30 time limit — expect 4-5 innings, 6th unlikely</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="n"/>
-      <c r="F3" s="4" t="n"/>
-      <c r="G3" s="4" t="n"/>
-      <c r="H3" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -1597,13 +2077,6 @@
           <t>Zack Martini (Inn 1-2) → Blake Lasita (Inn 3-4) → Owen Niemer (Inn 5-6 if needed)</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n"/>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
-      <c r="E6" s="7" t="n"/>
-      <c r="F6" s="7" t="n"/>
-      <c r="G6" s="7" t="n"/>
-      <c r="H6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
@@ -1611,13 +2084,6 @@
           <t>CATCHING: Charlie Ruther catches all innings (best 9U catcher, not pitching this game)</t>
         </is>
       </c>
-      <c r="B7" s="9" t="n"/>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="9" t="n"/>
-      <c r="E7" s="9" t="n"/>
-      <c r="F7" s="9" t="n"/>
-      <c r="G7" s="9" t="n"/>
-      <c r="H7" s="9" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -2458,60 +2924,1890 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
+          <t>ROSTER CHECK</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="21" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="B54" s="21" t="inlineStr">
+        <is>
+          <t>Inning 1</t>
+        </is>
+      </c>
+      <c r="C54" s="21" t="inlineStr">
+        <is>
+          <t>Inning 2</t>
+        </is>
+      </c>
+      <c r="D54" s="21" t="inlineStr">
+        <is>
+          <t>Inning 3</t>
+        </is>
+      </c>
+      <c r="E54" s="21" t="inlineStr">
+        <is>
+          <t>Inning 4</t>
+        </is>
+      </c>
+      <c r="F54" s="21" t="inlineStr">
+        <is>
+          <t>Inning 5 *</t>
+        </is>
+      </c>
+      <c r="G54" s="21" t="inlineStr">
+        <is>
+          <t>Inning 6 *</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="22" t="inlineStr">
+        <is>
+          <t>Porter</t>
+        </is>
+      </c>
+      <c r="B55" s="23">
+        <f>IF(COUNTIF(B$25:B$35,$A55)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="C55" s="23">
+        <f>IF(COUNTIF(C$25:C$35,$A55)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="D55" s="23">
+        <f>IF(COUNTIF(D$25:D$35,$A55)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="E55" s="23">
+        <f>IF(COUNTIF(E$25:E$35,$A55)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="F55" s="23">
+        <f>IF(COUNTIF(F$25:F$35,$A55)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="G55" s="23">
+        <f>IF(COUNTIF(G$25:G$35,$A55)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="22" t="inlineStr">
+        <is>
+          <t>Zack</t>
+        </is>
+      </c>
+      <c r="B56" s="23">
+        <f>IF(COUNTIF(B$25:B$35,$A56)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="C56" s="23">
+        <f>IF(COUNTIF(C$25:C$35,$A56)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="D56" s="23">
+        <f>IF(COUNTIF(D$25:D$35,$A56)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="E56" s="23">
+        <f>IF(COUNTIF(E$25:E$35,$A56)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="F56" s="23">
+        <f>IF(COUNTIF(F$25:F$35,$A56)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="G56" s="23">
+        <f>IF(COUNTIF(G$25:G$35,$A56)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="22" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="B57" s="23">
+        <f>IF(COUNTIF(B$25:B$35,$A57)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="C57" s="23">
+        <f>IF(COUNTIF(C$25:C$35,$A57)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="D57" s="23">
+        <f>IF(COUNTIF(D$25:D$35,$A57)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="E57" s="23">
+        <f>IF(COUNTIF(E$25:E$35,$A57)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="F57" s="23">
+        <f>IF(COUNTIF(F$25:F$35,$A57)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="G57" s="23">
+        <f>IF(COUNTIF(G$25:G$35,$A57)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="22" t="inlineStr">
+        <is>
+          <t>Crew</t>
+        </is>
+      </c>
+      <c r="B58" s="23">
+        <f>IF(COUNTIF(B$25:B$35,$A58)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="C58" s="23">
+        <f>IF(COUNTIF(C$25:C$35,$A58)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="D58" s="23">
+        <f>IF(COUNTIF(D$25:D$35,$A58)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="E58" s="23">
+        <f>IF(COUNTIF(E$25:E$35,$A58)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="F58" s="23">
+        <f>IF(COUNTIF(F$25:F$35,$A58)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="G58" s="23">
+        <f>IF(COUNTIF(G$25:G$35,$A58)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="22" t="inlineStr">
+        <is>
+          <t>Grayson</t>
+        </is>
+      </c>
+      <c r="B59" s="23">
+        <f>IF(COUNTIF(B$25:B$35,$A59)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="C59" s="23">
+        <f>IF(COUNTIF(C$25:C$35,$A59)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="D59" s="23">
+        <f>IF(COUNTIF(D$25:D$35,$A59)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="E59" s="23">
+        <f>IF(COUNTIF(E$25:E$35,$A59)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="F59" s="23">
+        <f>IF(COUNTIF(F$25:F$35,$A59)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="G59" s="23">
+        <f>IF(COUNTIF(G$25:G$35,$A59)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="22" t="inlineStr">
+        <is>
+          <t>Lasita</t>
+        </is>
+      </c>
+      <c r="B60" s="23">
+        <f>IF(COUNTIF(B$25:B$35,$A60)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="C60" s="23">
+        <f>IF(COUNTIF(C$25:C$35,$A60)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="D60" s="23">
+        <f>IF(COUNTIF(D$25:D$35,$A60)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="E60" s="23">
+        <f>IF(COUNTIF(E$25:E$35,$A60)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="F60" s="23">
+        <f>IF(COUNTIF(F$25:F$35,$A60)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="G60" s="23">
+        <f>IF(COUNTIF(G$25:G$35,$A60)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="22" t="inlineStr">
+        <is>
+          <t>Lukas</t>
+        </is>
+      </c>
+      <c r="B61" s="23">
+        <f>IF(COUNTIF(B$25:B$35,$A61)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="C61" s="23">
+        <f>IF(COUNTIF(C$25:C$35,$A61)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="D61" s="23">
+        <f>IF(COUNTIF(D$25:D$35,$A61)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="E61" s="23">
+        <f>IF(COUNTIF(E$25:E$35,$A61)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="F61" s="23">
+        <f>IF(COUNTIF(F$25:F$35,$A61)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="G61" s="23">
+        <f>IF(COUNTIF(G$25:G$35,$A61)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="22" t="inlineStr">
+        <is>
+          <t>Mason</t>
+        </is>
+      </c>
+      <c r="B62" s="23">
+        <f>IF(COUNTIF(B$25:B$35,$A62)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="C62" s="23">
+        <f>IF(COUNTIF(C$25:C$35,$A62)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="D62" s="23">
+        <f>IF(COUNTIF(D$25:D$35,$A62)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="E62" s="23">
+        <f>IF(COUNTIF(E$25:E$35,$A62)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="F62" s="23">
+        <f>IF(COUNTIF(F$25:F$35,$A62)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="G62" s="23">
+        <f>IF(COUNTIF(G$25:G$35,$A62)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="22" t="inlineStr">
+        <is>
+          <t>Kayson</t>
+        </is>
+      </c>
+      <c r="B63" s="23">
+        <f>IF(COUNTIF(B$25:B$35,$A63)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="C63" s="23">
+        <f>IF(COUNTIF(C$25:C$35,$A63)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="D63" s="23">
+        <f>IF(COUNTIF(D$25:D$35,$A63)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="E63" s="23">
+        <f>IF(COUNTIF(E$25:E$35,$A63)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="F63" s="23">
+        <f>IF(COUNTIF(F$25:F$35,$A63)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="G63" s="23">
+        <f>IF(COUNTIF(G$25:G$35,$A63)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="22" t="inlineStr">
+        <is>
+          <t>Owen</t>
+        </is>
+      </c>
+      <c r="B64" s="23">
+        <f>IF(COUNTIF(B$25:B$35,$A64)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="C64" s="23">
+        <f>IF(COUNTIF(C$25:C$35,$A64)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="D64" s="23">
+        <f>IF(COUNTIF(D$25:D$35,$A64)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="E64" s="23">
+        <f>IF(COUNTIF(E$25:E$35,$A64)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="F64" s="23">
+        <f>IF(COUNTIF(F$25:F$35,$A64)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="G64" s="23">
+        <f>IF(COUNTIF(G$25:G$35,$A64)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="22" t="inlineStr">
+        <is>
+          <t>Charlie</t>
+        </is>
+      </c>
+      <c r="B65" s="23">
+        <f>IF(COUNTIF(B$25:B$35,$A65)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="C65" s="23">
+        <f>IF(COUNTIF(C$25:C$35,$A65)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="D65" s="23">
+        <f>IF(COUNTIF(D$25:D$35,$A65)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="E65" s="23">
+        <f>IF(COUNTIF(E$25:E$35,$A65)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="F65" s="23">
+        <f>IF(COUNTIF(F$25:F$35,$A65)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="G65" s="23">
+        <f>IF(COUNTIF(G$25:G$35,$A65)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="24" t="inlineStr">
+        <is>
+          <t>Missing Count</t>
+        </is>
+      </c>
+      <c r="B66" s="25">
+        <f>COUNTIF(B55:B65,"MISSING")</f>
+        <v/>
+      </c>
+      <c r="C66" s="25">
+        <f>COUNTIF(C55:C65,"MISSING")</f>
+        <v/>
+      </c>
+      <c r="D66" s="25">
+        <f>COUNTIF(D55:D65,"MISSING")</f>
+        <v/>
+      </c>
+      <c r="E66" s="25">
+        <f>COUNTIF(E55:E65,"MISSING")</f>
+        <v/>
+      </c>
+      <c r="F66" s="25">
+        <f>COUNTIF(F55:F65,"MISSING")</f>
+        <v/>
+      </c>
+      <c r="G66" s="25">
+        <f>COUNTIF(G55:G65,"MISSING")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="26" t="inlineStr">
+        <is>
+          <t>(Each inning should have exactly 2 missing = bench)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
           <t>NOTES</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="20" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="20" t="inlineStr">
         <is>
           <t>• 1:30 time limit — best pitchers front-loaded in innings 1-4</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="20" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="20" t="inlineStr">
         <is>
           <t>• No player sits more than 2 innings | No player sits back-to-back</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="20" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="20" t="inlineStr">
         <is>
           <t>• Charlie behind the plate for stealing situations (9U live stealing)</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="20" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="20" t="inlineStr">
         <is>
           <t>• Batting order stays the same regardless of field position</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="20" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="20" t="inlineStr">
         <is>
           <t>• Zack (#1 pitcher) leads the big game — Crew covers SS when Zack pitches</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="7">
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A56:H56"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A55:H55"/>
     <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A57:H57"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A54:H54"/>
-    <mergeCell ref="A58:H58"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="A37:H37"/>
     <mergeCell ref="A6:H6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H76"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>GAME: Yeager vs Cincinnati Raiders</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="27" t="inlineStr">
+        <is>
+          <t>Wednesday, March 25 | TBD Time &amp; Field</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>1:30 time limit — expect 4-5 innings, 6th unlikely</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>PITCHING PLAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>Zack Martini (Inn 1-2) → Porter Mills (Inn 3-4) → Charlie Ruther (Inn 5-6 if needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="27" t="inlineStr">
+        <is>
+          <t>CATCHING: Charlie Ruther catches Inn 1-4 | Mason Floyd catches Inn 5-6 (when Charlie pitches)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>BATTING ORDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="21" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>Jersey</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr"/>
+      <c r="E10" s="21" t="inlineStr"/>
+      <c r="F10" s="21" t="inlineStr"/>
+      <c r="G10" s="21" t="inlineStr"/>
+      <c r="H10" s="21" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" s="29" t="inlineStr">
+        <is>
+          <t>Lukas Adams</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="B12" s="29" t="inlineStr">
+        <is>
+          <t>Zack Martini</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>#21</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" s="29" t="inlineStr">
+        <is>
+          <t>Crew Powers</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="B14" s="29" t="inlineStr">
+        <is>
+          <t>Grayson Neville</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="B15" s="29" t="inlineStr">
+        <is>
+          <t>Charlie Ruther</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>#15</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="B16" s="29" t="inlineStr">
+        <is>
+          <t>Blake Lasita</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="B17" s="29" t="inlineStr">
+        <is>
+          <t>Porter Mills</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="B18" s="29" t="inlineStr">
+        <is>
+          <t>Kayson Sander</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>#56</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="B19" s="29" t="inlineStr">
+        <is>
+          <t>Alex Todd</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="B20" s="29" t="inlineStr">
+        <is>
+          <t>Mason Floyd</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>#11</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="B21" s="29" t="inlineStr">
+        <is>
+          <t>Owen Niemer</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="inlineStr">
+        <is>
+          <t>#17</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>FIELD POSITIONS BY INNING</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="21" t="inlineStr">
+        <is>
+          <t>Position</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>Inning 1</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>Inning 2</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>Inning 3</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>Inning 4</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
+        <is>
+          <t>Inning 5 *</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
+        <is>
+          <t>Inning 6 *</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="22" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>Zack</t>
+        </is>
+      </c>
+      <c r="C25" s="23" t="inlineStr">
+        <is>
+          <t>Zack</t>
+        </is>
+      </c>
+      <c r="D25" s="23" t="inlineStr">
+        <is>
+          <t>Porter</t>
+        </is>
+      </c>
+      <c r="E25" s="23" t="inlineStr">
+        <is>
+          <t>Porter</t>
+        </is>
+      </c>
+      <c r="F25" s="23" t="inlineStr">
+        <is>
+          <t>Charlie</t>
+        </is>
+      </c>
+      <c r="G25" s="23" t="inlineStr">
+        <is>
+          <t>Charlie</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="22" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>Charlie</t>
+        </is>
+      </c>
+      <c r="C26" s="23" t="inlineStr">
+        <is>
+          <t>Charlie</t>
+        </is>
+      </c>
+      <c r="D26" s="23" t="inlineStr">
+        <is>
+          <t>Charlie</t>
+        </is>
+      </c>
+      <c r="E26" s="23" t="inlineStr">
+        <is>
+          <t>Charlie</t>
+        </is>
+      </c>
+      <c r="F26" s="23" t="inlineStr">
+        <is>
+          <t>Mason</t>
+        </is>
+      </c>
+      <c r="G26" s="23" t="inlineStr">
+        <is>
+          <t>Mason</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="22" t="inlineStr">
+        <is>
+          <t>1B</t>
+        </is>
+      </c>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>Lukas</t>
+        </is>
+      </c>
+      <c r="C27" s="23" t="inlineStr">
+        <is>
+          <t>Lukas</t>
+        </is>
+      </c>
+      <c r="D27" s="23" t="inlineStr">
+        <is>
+          <t>Lukas</t>
+        </is>
+      </c>
+      <c r="E27" s="23" t="inlineStr">
+        <is>
+          <t>Lukas</t>
+        </is>
+      </c>
+      <c r="F27" s="23" t="inlineStr">
+        <is>
+          <t>Porter</t>
+        </is>
+      </c>
+      <c r="G27" s="23" t="inlineStr">
+        <is>
+          <t>Porter</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="22" t="inlineStr">
+        <is>
+          <t>2B</t>
+        </is>
+      </c>
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>Grayson</t>
+        </is>
+      </c>
+      <c r="C28" s="23" t="inlineStr">
+        <is>
+          <t>Grayson</t>
+        </is>
+      </c>
+      <c r="D28" s="23" t="inlineStr">
+        <is>
+          <t>Grayson</t>
+        </is>
+      </c>
+      <c r="E28" s="23" t="inlineStr">
+        <is>
+          <t>Grayson</t>
+        </is>
+      </c>
+      <c r="F28" s="23" t="inlineStr">
+        <is>
+          <t>Grayson</t>
+        </is>
+      </c>
+      <c r="G28" s="23" t="inlineStr">
+        <is>
+          <t>Kayson</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="22" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>Lasita</t>
+        </is>
+      </c>
+      <c r="C29" s="23" t="inlineStr">
+        <is>
+          <t>Lasita</t>
+        </is>
+      </c>
+      <c r="D29" s="23" t="inlineStr">
+        <is>
+          <t>Lasita</t>
+        </is>
+      </c>
+      <c r="E29" s="23" t="inlineStr">
+        <is>
+          <t>Lasita</t>
+        </is>
+      </c>
+      <c r="F29" s="23" t="inlineStr">
+        <is>
+          <t>Lasita</t>
+        </is>
+      </c>
+      <c r="G29" s="23" t="inlineStr">
+        <is>
+          <t>Lasita</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="22" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>Crew</t>
+        </is>
+      </c>
+      <c r="C30" s="23" t="inlineStr">
+        <is>
+          <t>Crew</t>
+        </is>
+      </c>
+      <c r="D30" s="23" t="inlineStr">
+        <is>
+          <t>Zack</t>
+        </is>
+      </c>
+      <c r="E30" s="23" t="inlineStr">
+        <is>
+          <t>Zack</t>
+        </is>
+      </c>
+      <c r="F30" s="23" t="inlineStr">
+        <is>
+          <t>Zack</t>
+        </is>
+      </c>
+      <c r="G30" s="23" t="inlineStr">
+        <is>
+          <t>Zack</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="22" t="inlineStr">
+        <is>
+          <t>LF</t>
+        </is>
+      </c>
+      <c r="B31" s="23" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C31" s="23" t="inlineStr">
+        <is>
+          <t>Porter</t>
+        </is>
+      </c>
+      <c r="D31" s="23" t="inlineStr">
+        <is>
+          <t>Crew</t>
+        </is>
+      </c>
+      <c r="E31" s="23" t="inlineStr">
+        <is>
+          <t>Crew</t>
+        </is>
+      </c>
+      <c r="F31" s="23" t="inlineStr">
+        <is>
+          <t>Crew</t>
+        </is>
+      </c>
+      <c r="G31" s="23" t="inlineStr">
+        <is>
+          <t>Crew</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="22" t="inlineStr">
+        <is>
+          <t>CF</t>
+        </is>
+      </c>
+      <c r="B32" s="23" t="inlineStr">
+        <is>
+          <t>Owen</t>
+        </is>
+      </c>
+      <c r="C32" s="23" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="D32" s="23" t="inlineStr">
+        <is>
+          <t>Owen</t>
+        </is>
+      </c>
+      <c r="E32" s="23" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="F32" s="23" t="inlineStr">
+        <is>
+          <t>Owen</t>
+        </is>
+      </c>
+      <c r="G32" s="23" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="22" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B33" s="23" t="inlineStr">
+        <is>
+          <t>Kayson</t>
+        </is>
+      </c>
+      <c r="C33" s="23" t="inlineStr">
+        <is>
+          <t>Mason</t>
+        </is>
+      </c>
+      <c r="D33" s="23" t="inlineStr">
+        <is>
+          <t>Kayson</t>
+        </is>
+      </c>
+      <c r="E33" s="23" t="inlineStr">
+        <is>
+          <t>Owen</t>
+        </is>
+      </c>
+      <c r="F33" s="23" t="inlineStr">
+        <is>
+          <t>Kayson</t>
+        </is>
+      </c>
+      <c r="G33" s="23" t="inlineStr">
+        <is>
+          <t>Grayson</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="22" t="inlineStr">
+        <is>
+          <t>BN</t>
+        </is>
+      </c>
+      <c r="B34" s="23" t="inlineStr">
+        <is>
+          <t>Porter</t>
+        </is>
+      </c>
+      <c r="C34" s="23" t="inlineStr">
+        <is>
+          <t>Owen</t>
+        </is>
+      </c>
+      <c r="D34" s="23" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="E34" s="23" t="inlineStr">
+        <is>
+          <t>Mason</t>
+        </is>
+      </c>
+      <c r="F34" s="23" t="inlineStr">
+        <is>
+          <t>Lukas</t>
+        </is>
+      </c>
+      <c r="G34" s="23" t="inlineStr">
+        <is>
+          <t>Owen</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="22" t="inlineStr">
+        <is>
+          <t>BN</t>
+        </is>
+      </c>
+      <c r="B35" s="23" t="inlineStr">
+        <is>
+          <t>Mason</t>
+        </is>
+      </c>
+      <c r="C35" s="23" t="inlineStr">
+        <is>
+          <t>Kayson</t>
+        </is>
+      </c>
+      <c r="D35" s="23" t="inlineStr">
+        <is>
+          <t>Mason</t>
+        </is>
+      </c>
+      <c r="E35" s="23" t="inlineStr">
+        <is>
+          <t>Kayson</t>
+        </is>
+      </c>
+      <c r="F35" s="23" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="G35" s="23" t="inlineStr">
+        <is>
+          <t>Lukas</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="28" t="inlineStr">
+        <is>
+          <t>* Innings 5-6 may not be played due to time limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>BENCH COUNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="21" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="B40" s="21" t="inlineStr">
+        <is>
+          <t>Times Sat</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="inlineStr">
+        <is>
+          <t>Which Innings</t>
+        </is>
+      </c>
+      <c r="D40" s="21" t="inlineStr"/>
+      <c r="E40" s="21" t="inlineStr"/>
+      <c r="F40" s="21" t="inlineStr"/>
+      <c r="G40" s="21" t="inlineStr"/>
+      <c r="H40" s="21" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="22" t="inlineStr">
+        <is>
+          <t>Lukas</t>
+        </is>
+      </c>
+      <c r="B41" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" s="23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="22" t="inlineStr">
+        <is>
+          <t>Zack</t>
+        </is>
+      </c>
+      <c r="B42" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="22" t="inlineStr">
+        <is>
+          <t>Crew</t>
+        </is>
+      </c>
+      <c r="B43" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="22" t="inlineStr">
+        <is>
+          <t>Grayson</t>
+        </is>
+      </c>
+      <c r="B44" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="22" t="inlineStr">
+        <is>
+          <t>Charlie</t>
+        </is>
+      </c>
+      <c r="B45" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="22" t="inlineStr">
+        <is>
+          <t>Lasita</t>
+        </is>
+      </c>
+      <c r="B46" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="22" t="inlineStr">
+        <is>
+          <t>Porter</t>
+        </is>
+      </c>
+      <c r="B47" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="22" t="inlineStr">
+        <is>
+          <t>Kayson</t>
+        </is>
+      </c>
+      <c r="B48" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="C48" s="23" t="inlineStr">
+        <is>
+          <t>2, 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="22" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="B49" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="C49" s="23" t="inlineStr">
+        <is>
+          <t>3, 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="22" t="inlineStr">
+        <is>
+          <t>Mason</t>
+        </is>
+      </c>
+      <c r="B50" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="C50" s="23" t="inlineStr">
+        <is>
+          <t>1, 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="22" t="inlineStr">
+        <is>
+          <t>Owen</t>
+        </is>
+      </c>
+      <c r="B51" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="C51" s="23" t="inlineStr">
+        <is>
+          <t>2, 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>ROSTER CHECK</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="21" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="B54" s="21" t="inlineStr">
+        <is>
+          <t>Inning 1</t>
+        </is>
+      </c>
+      <c r="C54" s="21" t="inlineStr">
+        <is>
+          <t>Inning 2</t>
+        </is>
+      </c>
+      <c r="D54" s="21" t="inlineStr">
+        <is>
+          <t>Inning 3</t>
+        </is>
+      </c>
+      <c r="E54" s="21" t="inlineStr">
+        <is>
+          <t>Inning 4</t>
+        </is>
+      </c>
+      <c r="F54" s="21" t="inlineStr">
+        <is>
+          <t>Inning 5 *</t>
+        </is>
+      </c>
+      <c r="G54" s="21" t="inlineStr">
+        <is>
+          <t>Inning 6 *</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="22" t="inlineStr">
+        <is>
+          <t>Porter</t>
+        </is>
+      </c>
+      <c r="B55" s="23">
+        <f>IF(COUNTIF(B$25:B$35,$A55)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="C55" s="23">
+        <f>IF(COUNTIF(C$25:C$35,$A55)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="D55" s="23">
+        <f>IF(COUNTIF(D$25:D$35,$A55)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="E55" s="23">
+        <f>IF(COUNTIF(E$25:E$35,$A55)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="F55" s="23">
+        <f>IF(COUNTIF(F$25:F$35,$A55)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="G55" s="23">
+        <f>IF(COUNTIF(G$25:G$35,$A55)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="22" t="inlineStr">
+        <is>
+          <t>Zack</t>
+        </is>
+      </c>
+      <c r="B56" s="23">
+        <f>IF(COUNTIF(B$25:B$35,$A56)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="C56" s="23">
+        <f>IF(COUNTIF(C$25:C$35,$A56)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="D56" s="23">
+        <f>IF(COUNTIF(D$25:D$35,$A56)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="E56" s="23">
+        <f>IF(COUNTIF(E$25:E$35,$A56)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="F56" s="23">
+        <f>IF(COUNTIF(F$25:F$35,$A56)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="G56" s="23">
+        <f>IF(COUNTIF(G$25:G$35,$A56)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="22" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="B57" s="23">
+        <f>IF(COUNTIF(B$25:B$35,$A57)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="C57" s="23">
+        <f>IF(COUNTIF(C$25:C$35,$A57)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="D57" s="23">
+        <f>IF(COUNTIF(D$25:D$35,$A57)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="E57" s="23">
+        <f>IF(COUNTIF(E$25:E$35,$A57)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="F57" s="23">
+        <f>IF(COUNTIF(F$25:F$35,$A57)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="G57" s="23">
+        <f>IF(COUNTIF(G$25:G$35,$A57)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="22" t="inlineStr">
+        <is>
+          <t>Crew</t>
+        </is>
+      </c>
+      <c r="B58" s="23">
+        <f>IF(COUNTIF(B$25:B$35,$A58)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="C58" s="23">
+        <f>IF(COUNTIF(C$25:C$35,$A58)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="D58" s="23">
+        <f>IF(COUNTIF(D$25:D$35,$A58)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="E58" s="23">
+        <f>IF(COUNTIF(E$25:E$35,$A58)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="F58" s="23">
+        <f>IF(COUNTIF(F$25:F$35,$A58)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="G58" s="23">
+        <f>IF(COUNTIF(G$25:G$35,$A58)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="22" t="inlineStr">
+        <is>
+          <t>Grayson</t>
+        </is>
+      </c>
+      <c r="B59" s="23">
+        <f>IF(COUNTIF(B$25:B$35,$A59)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="C59" s="23">
+        <f>IF(COUNTIF(C$25:C$35,$A59)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="D59" s="23">
+        <f>IF(COUNTIF(D$25:D$35,$A59)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="E59" s="23">
+        <f>IF(COUNTIF(E$25:E$35,$A59)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="F59" s="23">
+        <f>IF(COUNTIF(F$25:F$35,$A59)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="G59" s="23">
+        <f>IF(COUNTIF(G$25:G$35,$A59)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="22" t="inlineStr">
+        <is>
+          <t>Lasita</t>
+        </is>
+      </c>
+      <c r="B60" s="23">
+        <f>IF(COUNTIF(B$25:B$35,$A60)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="C60" s="23">
+        <f>IF(COUNTIF(C$25:C$35,$A60)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="D60" s="23">
+        <f>IF(COUNTIF(D$25:D$35,$A60)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="E60" s="23">
+        <f>IF(COUNTIF(E$25:E$35,$A60)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="F60" s="23">
+        <f>IF(COUNTIF(F$25:F$35,$A60)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="G60" s="23">
+        <f>IF(COUNTIF(G$25:G$35,$A60)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="22" t="inlineStr">
+        <is>
+          <t>Lukas</t>
+        </is>
+      </c>
+      <c r="B61" s="23">
+        <f>IF(COUNTIF(B$25:B$35,$A61)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="C61" s="23">
+        <f>IF(COUNTIF(C$25:C$35,$A61)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="D61" s="23">
+        <f>IF(COUNTIF(D$25:D$35,$A61)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="E61" s="23">
+        <f>IF(COUNTIF(E$25:E$35,$A61)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="F61" s="23">
+        <f>IF(COUNTIF(F$25:F$35,$A61)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="G61" s="23">
+        <f>IF(COUNTIF(G$25:G$35,$A61)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="22" t="inlineStr">
+        <is>
+          <t>Mason</t>
+        </is>
+      </c>
+      <c r="B62" s="23">
+        <f>IF(COUNTIF(B$25:B$35,$A62)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="C62" s="23">
+        <f>IF(COUNTIF(C$25:C$35,$A62)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="D62" s="23">
+        <f>IF(COUNTIF(D$25:D$35,$A62)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="E62" s="23">
+        <f>IF(COUNTIF(E$25:E$35,$A62)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="F62" s="23">
+        <f>IF(COUNTIF(F$25:F$35,$A62)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="G62" s="23">
+        <f>IF(COUNTIF(G$25:G$35,$A62)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="22" t="inlineStr">
+        <is>
+          <t>Kayson</t>
+        </is>
+      </c>
+      <c r="B63" s="23">
+        <f>IF(COUNTIF(B$25:B$35,$A63)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="C63" s="23">
+        <f>IF(COUNTIF(C$25:C$35,$A63)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="D63" s="23">
+        <f>IF(COUNTIF(D$25:D$35,$A63)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="E63" s="23">
+        <f>IF(COUNTIF(E$25:E$35,$A63)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="F63" s="23">
+        <f>IF(COUNTIF(F$25:F$35,$A63)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="G63" s="23">
+        <f>IF(COUNTIF(G$25:G$35,$A63)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="22" t="inlineStr">
+        <is>
+          <t>Owen</t>
+        </is>
+      </c>
+      <c r="B64" s="23">
+        <f>IF(COUNTIF(B$25:B$35,$A64)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="C64" s="23">
+        <f>IF(COUNTIF(C$25:C$35,$A64)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="D64" s="23">
+        <f>IF(COUNTIF(D$25:D$35,$A64)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="E64" s="23">
+        <f>IF(COUNTIF(E$25:E$35,$A64)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="F64" s="23">
+        <f>IF(COUNTIF(F$25:F$35,$A64)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="G64" s="23">
+        <f>IF(COUNTIF(G$25:G$35,$A64)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="22" t="inlineStr">
+        <is>
+          <t>Charlie</t>
+        </is>
+      </c>
+      <c r="B65" s="23">
+        <f>IF(COUNTIF(B$25:B$35,$A65)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="C65" s="23">
+        <f>IF(COUNTIF(C$25:C$35,$A65)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="D65" s="23">
+        <f>IF(COUNTIF(D$25:D$35,$A65)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="E65" s="23">
+        <f>IF(COUNTIF(E$25:E$35,$A65)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="F65" s="23">
+        <f>IF(COUNTIF(F$25:F$35,$A65)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+      <c r="G65" s="23">
+        <f>IF(COUNTIF(G$25:G$35,$A65)&gt;0,"✓","MISSING")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="24" t="inlineStr">
+        <is>
+          <t>Missing Count</t>
+        </is>
+      </c>
+      <c r="B66" s="25">
+        <f>COUNTIF(B55:B65,"MISSING")</f>
+        <v/>
+      </c>
+      <c r="C66" s="25">
+        <f>COUNTIF(C55:C65,"MISSING")</f>
+        <v/>
+      </c>
+      <c r="D66" s="25">
+        <f>COUNTIF(D55:D65,"MISSING")</f>
+        <v/>
+      </c>
+      <c r="E66" s="25">
+        <f>COUNTIF(E55:E65,"MISSING")</f>
+        <v/>
+      </c>
+      <c r="F66" s="25">
+        <f>COUNTIF(F55:F65,"MISSING")</f>
+        <v/>
+      </c>
+      <c r="G66" s="25">
+        <f>COUNTIF(G55:G65,"MISSING")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="26" t="inlineStr">
+        <is>
+          <t>(Each inning should have exactly 2 missing = bench)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>NOTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="27" t="inlineStr">
+        <is>
+          <t>• 1:30 time limit — Zack leads innings 1-2 to control pace and keep it close early</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="27" t="inlineStr">
+        <is>
+          <t>• Lesson from bracket play: get your ace on the mound early, not behind the plate</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="27" t="inlineStr">
+        <is>
+          <t>• No player sits more than 2 innings | No player sits back-to-back</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="27" t="inlineStr">
+        <is>
+          <t>• Charlie behind the plate for stealing situations (9U live stealing)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="27" t="inlineStr">
+        <is>
+          <t>• Batting order stays the same regardless of field position</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="27" t="inlineStr">
+        <is>
+          <t>• Crew covers SS when Zack pitches (proven combo from bracket play)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="27" t="inlineStr">
+        <is>
+          <t>• If game gets tight mid-game, Zack is available to re-enter on the mound</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="19">
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A39:H39"/>
+    <mergeCell ref="A73:H73"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="A70:H70"/>
+    <mergeCell ref="A69:H69"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A75:H75"/>
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="A74:H74"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A71:H71"/>
+    <mergeCell ref="A76:H76"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A53:H53"/>
+    <mergeCell ref="A72:H72"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>